--- a/reports/monthly/ECOM-MMSNG_DAILY_ORDER_H6183001_202608_MONTHLY.xlsx
+++ b/reports/monthly/ECOM-MMSNG_DAILY_ORDER_H6183001_202608_MONTHLY.xlsx
@@ -431,7 +431,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-Aug-24 00:57:11</t>
+          <t>2026-Aug-24 01:03:51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
